--- a/pangan.xlsx
+++ b/pangan.xlsx
@@ -25,9 +25,6 @@
     <t>Produktivitas_Padi</t>
   </si>
   <si>
-    <t>Produksi_Beras</t>
-  </si>
-  <si>
     <t>P0</t>
   </si>
   <si>
@@ -509,6 +506,9 @@
   </si>
   <si>
     <t>IKP</t>
+  </si>
+  <si>
+    <t>Produksi_Padi</t>
   </si>
 </sst>
 </file>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -891,30 +891,30 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3">
         <v>77.540000000000006</v>
@@ -949,7 +949,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3">
         <v>46.1</v>
@@ -984,7 +984,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3">
         <v>73.84</v>
@@ -1019,7 +1019,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3">
         <v>76.87</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="3">
         <v>77.19</v>
@@ -1089,7 +1089,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3">
         <v>69.08</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2">
         <v>78.27</v>
@@ -1159,7 +1159,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2">
         <v>84.72</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2">
         <v>76.69</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2">
         <v>80.83</v>
@@ -1264,7 +1264,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2">
         <v>77.12</v>
@@ -1299,7 +1299,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="2">
         <v>78.05</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2">
         <v>77.06</v>
@@ -1369,7 +1369,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2">
         <v>81.16</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2">
         <v>76.599999999999994</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2">
         <v>79.69</v>
@@ -1474,7 +1474,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2">
         <v>46.98</v>
@@ -1509,7 +1509,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2">
         <v>78.95</v>
@@ -1544,7 +1544,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2">
         <v>87.96</v>
@@ -1579,7 +1579,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2">
         <v>73.8</v>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="2">
         <v>78.05</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="2">
         <v>83.03</v>
@@ -1678,7 +1678,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="2">
         <v>41.12</v>
@@ -1713,7 +1713,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="2">
         <v>72.41</v>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2">
         <v>70.540000000000006</v>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2">
         <v>77.290000000000006</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2">
         <v>73.81</v>
@@ -1853,7 +1853,7 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="2">
         <v>78.14</v>
@@ -1888,7 +1888,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2">
         <v>84.33</v>
@@ -1923,7 +1923,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="2">
         <v>76.959999999999994</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="2">
         <v>76.650000000000006</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="2">
         <v>82.42</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="2">
         <v>82.5</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="2">
         <v>82.28</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="2">
         <v>86.2</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" s="2">
         <v>79.92</v>
@@ -2168,7 +2168,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38" s="2">
         <v>65.87</v>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" s="2">
         <v>81.16</v>
@@ -2238,7 +2238,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40" s="2">
         <v>75.319999999999993</v>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" s="2">
         <v>80.349999999999994</v>
@@ -2308,7 +2308,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42" s="2">
         <v>85.35</v>
@@ -2343,7 +2343,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="2">
         <v>78.37</v>
@@ -2378,7 +2378,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" s="2">
         <v>75.14</v>
@@ -2413,7 +2413,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" s="2">
         <v>76.75</v>
@@ -2448,7 +2448,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" s="2">
         <v>57.85</v>
@@ -2483,7 +2483,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B47" s="2">
         <v>80.3</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B48" s="2">
         <v>73.17</v>
@@ -2553,7 +2553,7 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B49" s="2">
         <v>65.349999999999994</v>
@@ -2588,7 +2588,7 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B50" s="2">
         <v>81.03</v>
@@ -2617,7 +2617,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B51" s="2">
         <v>74.59</v>
@@ -2652,7 +2652,7 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B52" s="2">
         <v>89.82</v>
@@ -2687,7 +2687,7 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" s="2">
         <v>77.31</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54" s="2">
         <v>90.25</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55" s="2">
         <v>88.22</v>
@@ -2792,7 +2792,7 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" s="2">
         <v>71.319999999999993</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B57" s="2">
         <v>66.12</v>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B58" s="2">
         <v>53.86</v>
@@ -2897,7 +2897,7 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B59" s="2">
         <v>86.71</v>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" s="2">
         <v>82.56</v>
@@ -2967,7 +2967,7 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B61" s="2">
         <v>82.05</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B62" s="2">
         <v>89.4</v>
@@ -3037,7 +3037,7 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B63" s="2">
         <v>85.08</v>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B64" s="2">
         <v>86.92</v>
@@ -3107,7 +3107,7 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B65" s="2">
         <v>82.59</v>
@@ -3142,7 +3142,7 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B66" s="2">
         <v>82.09</v>
@@ -3177,7 +3177,7 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B67" s="2">
         <v>85.6</v>
@@ -3212,7 +3212,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B68" s="2">
         <v>84.98</v>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B69" s="2">
         <v>80.91</v>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B70" s="2">
         <v>89.63</v>
@@ -3317,7 +3317,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B71" s="2">
         <v>92.9</v>
@@ -3352,7 +3352,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B72" s="2">
         <v>83.45</v>
@@ -3387,7 +3387,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B73" s="2">
         <v>87.05</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B74" s="2">
         <v>92.86</v>
@@ -3457,7 +3457,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B75" s="2">
         <v>89.33</v>
@@ -3492,7 +3492,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B76" s="2">
         <v>84.08</v>
@@ -3527,7 +3527,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B77" s="2">
         <v>73.8</v>
@@ -3562,7 +3562,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B78" s="2">
         <v>60.71</v>
@@ -3597,7 +3597,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B79" s="2">
         <v>69.3</v>
@@ -3632,7 +3632,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B80" s="2">
         <v>71.59</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B81" s="2">
         <v>77.06</v>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B82" s="2">
         <v>59.69</v>
@@ -3737,7 +3737,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B83" s="2">
         <v>58.88</v>
@@ -3772,7 +3772,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B84" s="2">
         <v>65.75</v>
@@ -3807,7 +3807,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B85" s="2">
         <v>68.67</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B86" s="2">
         <v>71.150000000000006</v>
@@ -3877,7 +3877,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B87" s="2">
         <v>92.2</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B88" s="2">
         <v>76.3</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B89" s="2">
         <v>83.76</v>
@@ -3979,7 +3979,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B90" s="2">
         <v>75.010000000000005</v>
@@ -4011,7 +4011,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B91" s="2">
         <v>65.64</v>
@@ -4043,7 +4043,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B92" s="2">
         <v>74.13</v>
@@ -4075,7 +4075,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B93" s="2">
         <v>68.510000000000005</v>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B94" s="2">
         <v>69.989999999999995</v>
@@ -4139,7 +4139,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B95" s="2">
         <v>69.599999999999994</v>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B96" s="2">
         <v>71.36</v>
@@ -4203,7 +4203,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B97" s="2">
         <v>73.39</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B98" s="2">
         <v>85.88</v>
@@ -4267,7 +4267,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B99" s="2">
         <v>87.06</v>
@@ -4299,7 +4299,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B100" s="4">
         <v>73.010000000000005</v>
@@ -4331,7 +4331,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B101" s="4">
         <v>79.540000000000006</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B102" s="4">
         <v>75.62</v>
@@ -4395,7 +4395,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B103" s="4">
         <v>75.19</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B104" s="4">
         <v>77.66</v>
@@ -4459,7 +4459,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B105" s="4">
         <v>79.48</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B106" s="4">
         <v>79.17</v>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B107" s="4">
         <v>75.37</v>
@@ -4555,7 +4555,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B108" s="4">
         <v>85.17</v>
@@ -4587,7 +4587,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B109" s="4">
         <v>77.55</v>
@@ -4619,7 +4619,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B110" s="4">
         <v>67.42</v>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B111" s="4">
         <v>78.790000000000006</v>
@@ -4683,7 +4683,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B112" s="4">
         <v>59.58</v>
@@ -4715,7 +4715,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B113" s="2">
         <v>83.62</v>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B114" s="2">
         <v>68.11</v>
@@ -4779,7 +4779,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B115" s="2">
         <v>57.79</v>
@@ -4811,7 +4811,7 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B116" s="2">
         <v>66.099999999999994</v>
@@ -4843,7 +4843,7 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B117" s="4">
         <v>74.91</v>
@@ -4875,7 +4875,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B118" s="4">
         <v>73.11</v>
@@ -4907,7 +4907,7 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B119" s="4">
         <v>72.62</v>
@@ -4939,7 +4939,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B120" s="4">
         <v>74.75</v>
@@ -4971,7 +4971,7 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B121" s="4">
         <v>71.61</v>
@@ -5003,7 +5003,7 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B122" s="4">
         <v>76.569999999999993</v>
@@ -5035,7 +5035,7 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B123" s="4">
         <v>77.06</v>
@@ -5067,7 +5067,7 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B124" s="4">
         <v>72.430000000000007</v>
@@ -5099,7 +5099,7 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B125" s="4">
         <v>62.14</v>
@@ -5131,7 +5131,7 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B126" s="2">
         <v>78.72</v>
@@ -5163,7 +5163,7 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B127" s="4">
         <v>76.180000000000007</v>
@@ -5198,7 +5198,7 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B128" s="4">
         <v>76.400000000000006</v>
@@ -5233,7 +5233,7 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B129" s="4">
         <v>84.46</v>
@@ -5268,7 +5268,7 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B130" s="4">
         <v>85.22</v>
@@ -5303,7 +5303,7 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B131" s="4">
         <v>84.93</v>
@@ -5338,7 +5338,7 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B132" s="4">
         <v>76.819999999999993</v>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B133" s="4">
         <v>79.61</v>
@@ -5408,7 +5408,7 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B134" s="4">
         <v>88.78</v>
@@ -5443,7 +5443,7 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B135" s="4">
         <v>80.849999999999994</v>
@@ -5478,7 +5478,7 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B136" s="4">
         <v>87.35</v>
@@ -5513,7 +5513,7 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B137" s="4">
         <v>88.18</v>
@@ -5548,7 +5548,7 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B138" s="4">
         <v>83.74</v>
@@ -5583,7 +5583,7 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B139" s="4">
         <v>75.77</v>
@@ -5618,7 +5618,7 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B140" s="2">
         <v>84.64</v>
@@ -5653,7 +5653,7 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B141" s="2">
         <v>85.78</v>
@@ -5688,7 +5688,7 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B142" s="4">
         <v>74.349999999999994</v>
@@ -5723,7 +5723,7 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B143" s="4">
         <v>62.34</v>
@@ -5758,7 +5758,7 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B144" s="4">
         <v>60.25</v>
@@ -5793,7 +5793,7 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B145" s="4">
         <v>60.38</v>
@@ -5828,7 +5828,7 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B146" s="4">
         <v>84.87</v>
@@ -5863,7 +5863,7 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B147" s="4">
         <v>62.02</v>
@@ -5898,7 +5898,7 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B148" s="2">
         <v>87.27</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B149" s="4">
         <v>62.68</v>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B150" s="4">
         <v>60.42</v>
@@ -5991,7 +5991,7 @@
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B151" s="4">
         <v>60.51</v>
@@ -6026,7 +6026,7 @@
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B152" s="4">
         <v>53.02</v>
@@ -6061,7 +6061,7 @@
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B153" s="4">
         <v>55.34</v>
@@ -6096,7 +6096,7 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B154" s="2">
         <v>88.83</v>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B155" s="2">
         <v>83.22</v>
